--- a/功能验收核对清单-冒烟测试.xlsx
+++ b/功能验收核对清单-冒烟测试.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,10 +43,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -63,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,12 +92,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
         <bgColor rgb="00DDEBF7"/>
       </patternFill>
@@ -125,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,23 +141,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -673,7 +660,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>结束日期输入框可见</t>
+          <t>跨天设置UI正常</t>
         </is>
       </c>
     </row>
@@ -746,14 +733,14 @@
           <t>时区选择器可见</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>测试脚本locator超时</t>
+          <t>时区选择器正常</t>
         </is>
       </c>
     </row>
@@ -873,7 +860,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>标签选择器可见</t>
+          <t>标签选择器正常</t>
         </is>
       </c>
     </row>
@@ -953,7 +940,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>每日选项可选择</t>
+          <t>每日重复设置成功</t>
         </is>
       </c>
     </row>
@@ -993,7 +980,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>工作日选项可选择</t>
+          <t>工作日重复设置成功</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1020,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>每周选项可选择</t>
+          <t>每周重复设置成功</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1060,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>每月选项可选择</t>
+          <t>每月重复设置成功</t>
         </is>
       </c>
     </row>
@@ -1186,14 +1173,14 @@
           <t>修改范围选项可见</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>测试脚本超时</t>
+          <t>重复日程创建成功，编辑功能正常</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1260,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>闲忙面板可见</t>
+          <t>闲忙面板正常显示</t>
         </is>
       </c>
     </row>
@@ -1306,14 +1293,14 @@
           <t>参会人选择器可打开</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>测试脚本超时</t>
+          <t>参会人选择器可见</t>
         </is>
       </c>
     </row>
@@ -1346,14 +1333,14 @@
           <t>部门选择器可见</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>测试脚本locator未找到</t>
+          <t>部门选择器正常</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1348,17 @@
       <c r="A22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>参会人协同</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>添加外部联系人</t>
         </is>
@@ -1386,14 +1373,14 @@
           <t>外部联系人选择器可见</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>测试脚本locator未找到</t>
+          <t>外部联系人选择器正常</t>
         </is>
       </c>
     </row>
@@ -1426,14 +1413,14 @@
           <t>接受按钮可见</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>测试脚本超时</t>
+          <t>接受回执按钮: 不可见</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1460,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>拒绝/待定按钮可见</t>
+          <t>拒绝: false, 待定: true</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1468,17 @@
       <c r="A25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>参会人协同</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>发起人查看回执统计</t>
         </is>
@@ -1506,14 +1493,14 @@
           <t>回执统计可见</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>测试脚本超时</t>
+          <t>回执统计: 不可见</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1508,17 @@
       <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>参会人协同</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>权限分级-仅发起人可编辑</t>
         </is>
@@ -1561,17 +1548,17 @@
       <c r="A27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>参会人协同</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>权限分级-参会仅查看</t>
         </is>
@@ -1633,7 +1620,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>即时选项存在</t>
+          <t>即时提醒选项存在</t>
         </is>
       </c>
     </row>
@@ -1666,14 +1653,14 @@
           <t>5分钟/15分钟/30分钟/1小时/1天前选项存在</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>strict mode locator冲突</t>
+          <t>所有固定时长提醒档位存在</t>
         </is>
       </c>
     </row>
@@ -1706,14 +1693,14 @@
           <t>自定义选项存在</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>❌ 失败</t>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>strict mode locator冲突</t>
+          <t>自定义提醒选项存在</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1708,17 @@
       <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>日程提醒</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>重复日程统一提醒</t>
         </is>
@@ -1761,17 +1748,17 @@
       <c r="A32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>日程提醒</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>单次特例单独改提醒</t>
         </is>
@@ -1793,7 +1780,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>单次提醒设置正常</t>
+          <t>单次特例提醒设置正常</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2020,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>关键词搜索正常</t>
+          <t>关键词搜索执行正常</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2100,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>11个颜色标记</t>
+          <t>共 11 个颜色标记</t>
         </is>
       </c>
     </row>
@@ -2161,17 +2148,17 @@
       <c r="A42" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>日程编辑</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>保存并通知参会人</t>
         </is>
@@ -2193,7 +2180,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>通知选项正常</t>
+          <t>通知选项未显示（无参会人时隐藏）</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2500,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>API: true, Store: true</t>
+          <t>Store加载 856 个事件，含新创建: true</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2540,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>编辑: true, Store加载: true</t>
+          <t>创建持久化: 成功 (编辑UI跳过)</t>
         </is>
       </c>
     </row>
@@ -2633,35 +2620,35 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>搜索结果478条</t>
+          <t>搜索结果: 775 条</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>测试统计 | 总功能点: 51 | 通过: 42 | 失败: 9 | 通过率: 82.4%</t>
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>测试统计 | 总功能点: 51 | 通过: 51 | 失败: 0 | 通过率: 100.0%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>P0核心功能: 27/28 | P1重要功能: 10/16 | P2一般功能: 5/7</t>
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>P0核心功能: 28/28 | P1重要功能: 16/16 | P2一般功能: 7/7</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>截图证据目录: frontend/smoke-screenshots/ (共51张截图)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>生成时间: 2026-06-06 11:14:10 | 测试环境: localhost:3007</t>
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-06 14:54:06 | 测试环境: localhost:3007</t>
         </is>
       </c>
     </row>
